--- a/supplementary/Table S2 - Symbiodiniaceae species.xlsx
+++ b/supplementary/Table S2 - Symbiodiniaceae species.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\S_Pistillata_Bet-Hedging\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DA880F-CD4C-44A1-8A85-ED25DE4DDB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247E2522-D0D8-4DC9-8A42-C53D6BF2066B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6585" yWindow="6765" windowWidth="26430" windowHeight="10065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6930" yWindow="7110" windowWidth="26430" windowHeight="10065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>Reference dataset</t>
   </si>
@@ -148,6 +148,21 @@
   </si>
   <si>
     <t>Cladocopium C15</t>
+  </si>
+  <si>
+    <r>
+      <t>Supplementary Table 2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Reference Symbiodiniaceae species, strains, and genomic databases utilized for read filtering, mapping, and comparative analyses. The table lists the taxonomic species/strain designations, corresponding legacy clade classifications (former clades A, B, C, D, and F), and official repository URLs or data access links (NCBI GenBank, OIST Marine Genomics, UQ eSpace, and ReefGenomics)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -208,7 +223,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -221,6 +236,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -503,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:C17"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.42578125" customWidth="1"/>
@@ -511,6 +529,13 @@
     <col min="3" max="3" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+    </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -664,6 +689,9 @@
     </row>
     <row r="17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" xr:uid="{96CD95FA-90F9-4AD0-85F8-9A5023A7D937}"/>
     <hyperlink ref="A5" r:id="rId2" xr:uid="{19558643-65A4-4E91-9F46-40479140E1F2}"/>
